--- a/data/sample_input/asset_data template.xlsx
+++ b/data/sample_input/asset_data template.xlsx
@@ -8,14 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Github Repositories\tool\data\sample_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089E5733-2AA5-4BF4-BF08-182AA52FEB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90500198-F927-4AEC-91DF-D6DAD3C0461A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{709B18CE-B3B4-4992-8722-EB4EEC6FDBE4}"/>
   </bookViews>
   <sheets>
     <sheet name="asset_data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">asset_data!$A$1:$F$62</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -43,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="148">
   <si>
     <t>INDEX</t>
   </si>
@@ -234,12 +250,6 @@
     <t>B04</t>
   </si>
   <si>
-    <t>Monitoring Server 01</t>
-  </si>
-  <si>
-    <t>Management Server 01</t>
-  </si>
-  <si>
     <t>TOR B04A</t>
   </si>
   <si>
@@ -280,13 +290,226 @@
   </si>
   <si>
     <t>TOR B05B</t>
+  </si>
+  <si>
+    <t>SNMP HOSTNAME</t>
+  </si>
+  <si>
+    <t>ComputeNode01</t>
+  </si>
+  <si>
+    <t>ComputeNode02</t>
+  </si>
+  <si>
+    <t>ComputeNode03</t>
+  </si>
+  <si>
+    <t>ComputeNode04</t>
+  </si>
+  <si>
+    <t>TORA01A</t>
+  </si>
+  <si>
+    <t>TORA01B</t>
+  </si>
+  <si>
+    <t>TORA02A</t>
+  </si>
+  <si>
+    <t>TORA02B</t>
+  </si>
+  <si>
+    <t>TORA03A</t>
+  </si>
+  <si>
+    <t>TORA03B</t>
+  </si>
+  <si>
+    <t>TORA04A</t>
+  </si>
+  <si>
+    <t>TORA04B</t>
+  </si>
+  <si>
+    <t>TORA05A</t>
+  </si>
+  <si>
+    <t>TORA05B</t>
+  </si>
+  <si>
+    <t>ComputeNode05</t>
+  </si>
+  <si>
+    <t>ComputeNode06</t>
+  </si>
+  <si>
+    <t>ComputeNode07</t>
+  </si>
+  <si>
+    <t>ComputeNode08</t>
+  </si>
+  <si>
+    <t>TORB01A</t>
+  </si>
+  <si>
+    <t>TORB01B</t>
+  </si>
+  <si>
+    <t>TORB02A</t>
+  </si>
+  <si>
+    <t>TORB02B</t>
+  </si>
+  <si>
+    <t>TORB03A</t>
+  </si>
+  <si>
+    <t>TORB03B</t>
+  </si>
+  <si>
+    <t>BackupServer01</t>
+  </si>
+  <si>
+    <t>TORB04A</t>
+  </si>
+  <si>
+    <t>TORB04B</t>
+  </si>
+  <si>
+    <t>SANControllerA</t>
+  </si>
+  <si>
+    <t>SANControllerB</t>
+  </si>
+  <si>
+    <t>CoreSwitch01</t>
+  </si>
+  <si>
+    <t>CoreSwitch02</t>
+  </si>
+  <si>
+    <t>SANSwitchA</t>
+  </si>
+  <si>
+    <t>SANSwitchB</t>
+  </si>
+  <si>
+    <t>TORB05A</t>
+  </si>
+  <si>
+    <t>TORB05B</t>
+  </si>
+  <si>
+    <t>VirtCluster01</t>
+  </si>
+  <si>
+    <t>VirtCluster02</t>
+  </si>
+  <si>
+    <t>VirtCluster03</t>
+  </si>
+  <si>
+    <t>VirtCluster04</t>
+  </si>
+  <si>
+    <t>VirtCluster05</t>
+  </si>
+  <si>
+    <t>VirtCluster06</t>
+  </si>
+  <si>
+    <t>VirtCluster07</t>
+  </si>
+  <si>
+    <t>VirtCluster08</t>
+  </si>
+  <si>
+    <t>AppServer01</t>
+  </si>
+  <si>
+    <t>AppServer02</t>
+  </si>
+  <si>
+    <t>DBServer01</t>
+  </si>
+  <si>
+    <t>DBServer02</t>
+  </si>
+  <si>
+    <t>AINode01</t>
+  </si>
+  <si>
+    <t>AINode02</t>
+  </si>
+  <si>
+    <t>KubeNode01</t>
+  </si>
+  <si>
+    <t>KubeNode02</t>
+  </si>
+  <si>
+    <t>KubeNode03</t>
+  </si>
+  <si>
+    <t>Mon Server 01</t>
+  </si>
+  <si>
+    <t>MonServer01</t>
+  </si>
+  <si>
+    <t>Mgmt Server 01</t>
+  </si>
+  <si>
+    <t>MgmtServer01</t>
+  </si>
+  <si>
+    <t>Compute Node 09</t>
+  </si>
+  <si>
+    <t>Compute Node 10</t>
+  </si>
+  <si>
+    <t>Compute Node 11</t>
+  </si>
+  <si>
+    <t>Compute Node 12</t>
+  </si>
+  <si>
+    <t>Virtualisation Cluster 09</t>
+  </si>
+  <si>
+    <t>Virtualisation Cluster 10</t>
+  </si>
+  <si>
+    <t>Virtualisation Cluster 11</t>
+  </si>
+  <si>
+    <t>ComputeNode09</t>
+  </si>
+  <si>
+    <t>ComputeNode10</t>
+  </si>
+  <si>
+    <t>ComputeNode11</t>
+  </si>
+  <si>
+    <t>ComputeNode12</t>
+  </si>
+  <si>
+    <t>VirtCluster09</t>
+  </si>
+  <si>
+    <t>VirtCluster10</t>
+  </si>
+  <si>
+    <t>VirtCluster11</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -426,6 +649,12 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
@@ -836,7 +1065,47 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1177,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF958A36-346A-4392-A336-5806CB7B488B}">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:H62"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6" style="2" bestFit="1" customWidth="1"/>
@@ -1186,10 +1455,12 @@
     <col min="4" max="4" width="5.453125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.26953125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.26953125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="8.7265625" style="1"/>
+    <col min="7" max="7" width="8.7265625" style="1"/>
+    <col min="8" max="8" width="20.36328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1208,8 +1479,11 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H1" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1228,8 +1502,11 @@
       <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H2" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1248,8 +1525,11 @@
       <c r="F3" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H3" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1268,8 +1548,11 @@
       <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H4" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1288,13 +1571,16 @@
       <c r="F5" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H5" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>7</v>
@@ -1308,13 +1594,16 @@
       <c r="F6" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H6" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>7</v>
@@ -1328,13 +1617,16 @@
       <c r="F7" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H7" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>7</v>
@@ -1348,13 +1640,16 @@
       <c r="F8" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H8" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>7</v>
@@ -1368,8 +1663,11 @@
       <c r="F9" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H9" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1388,8 +1686,11 @@
       <c r="F10" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H10" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1408,8 +1709,11 @@
       <c r="F11" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H11" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1428,8 +1732,11 @@
       <c r="F12" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H12" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1448,8 +1755,11 @@
       <c r="F13" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H13" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -1468,13 +1778,16 @@
       <c r="F14" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H14" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>7</v>
@@ -1488,13 +1801,16 @@
       <c r="F15" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H15" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>7</v>
@@ -1508,13 +1824,16 @@
       <c r="F16" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H16" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>7</v>
@@ -1528,8 +1847,11 @@
       <c r="F17" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H17" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -1548,8 +1870,11 @@
       <c r="F18" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H18" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1568,13 +1893,16 @@
       <c r="F19" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H19" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>7</v>
@@ -1588,13 +1916,16 @@
       <c r="F20" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H20" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>7</v>
@@ -1608,8 +1939,11 @@
       <c r="F21" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H21" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -1628,8 +1962,11 @@
       <c r="F22" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H22" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1648,8 +1985,11 @@
       <c r="F23" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H23" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -1668,8 +2008,11 @@
       <c r="F24" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H24" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1688,8 +2031,11 @@
       <c r="F25" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H25" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -1708,8 +2054,11 @@
       <c r="F26" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H26" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1728,8 +2077,11 @@
       <c r="F27" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H27" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -1748,8 +2100,11 @@
       <c r="F28" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H28" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1768,8 +2123,11 @@
       <c r="F29" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H29" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -1788,8 +2146,11 @@
       <c r="F30" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H30" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1808,8 +2169,11 @@
       <c r="F31" s="2" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H31" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -1828,8 +2192,11 @@
       <c r="F32" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H32" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1848,13 +2215,16 @@
       <c r="F33" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H33" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>41</v>
+        <v>134</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>42</v>
@@ -1868,13 +2238,16 @@
       <c r="F34" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H34" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>44</v>
+        <v>135</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>42</v>
@@ -1888,13 +2261,16 @@
       <c r="F35" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H35" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>45</v>
+        <v>136</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>42</v>
@@ -1908,13 +2284,16 @@
       <c r="F36" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H36" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>46</v>
+        <v>137</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>42</v>
@@ -1928,8 +2307,11 @@
       <c r="F37" s="2" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H37" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -1948,8 +2330,11 @@
       <c r="F38" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H38" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1968,13 +2353,16 @@
       <c r="F39" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H39" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>42</v>
@@ -1988,13 +2376,16 @@
       <c r="F40" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H40" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>51</v>
+        <v>139</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>42</v>
@@ -2008,13 +2399,16 @@
       <c r="F41" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H41" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>42</v>
@@ -2028,8 +2422,11 @@
       <c r="F42" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H42" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2048,8 +2445,11 @@
       <c r="F43" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H43" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -2068,8 +2468,11 @@
       <c r="F44" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H44" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2088,8 +2491,11 @@
       <c r="F45" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H45" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -2108,8 +2514,11 @@
       <c r="F46" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H46" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2128,8 +2537,11 @@
       <c r="F47" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H47" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -2148,8 +2560,11 @@
       <c r="F48" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H48" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2168,8 +2583,11 @@
       <c r="F49" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H49" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -2188,13 +2606,16 @@
       <c r="F50" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H50" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>42</v>
@@ -2208,13 +2629,16 @@
       <c r="F51" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H51" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>64</v>
+        <v>132</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>42</v>
@@ -2228,13 +2652,16 @@
       <c r="F52" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H52" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>42</v>
@@ -2248,13 +2675,16 @@
       <c r="F53" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H53" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>42</v>
@@ -2268,139 +2698,160 @@
       <c r="F54" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H54" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E55" s="2">
         <v>1</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E56" s="2">
         <v>5</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E57" s="2">
         <v>35</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E58" s="2">
         <v>36</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E59" s="2">
         <v>38</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E60" s="2">
         <v>39</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+        <v>73</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E61" s="2">
         <v>41</v>
@@ -2408,19 +2859,22 @@
       <c r="F61" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="H61" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>42</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E62" s="2">
         <v>42</v>
@@ -2428,9 +2882,20 @@
       <c r="F62" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="H62" s="2" t="s">
+        <v>112</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F62" xr:uid="{BF958A36-346A-4392-A336-5806CB7B488B}"/>
+  <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H1:H1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/sample_input/asset_data template.xlsx
+++ b/data/sample_input/asset_data template.xlsx
@@ -1065,27 +1065,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2890,10 +2870,10 @@
   <autoFilter ref="A1:F62" xr:uid="{BF958A36-346A-4392-A336-5806CB7B488B}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>

--- a/data/sample_input/asset_data template.xlsx
+++ b/data/sample_input/asset_data template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_Github Repositories\tool\data\sample_input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90500198-F927-4AEC-91DF-D6DAD3C0461A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E0D7DD6-A488-4DB7-9B31-2ECC9BAE70EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{709B18CE-B3B4-4992-8722-EB4EEC6FDBE4}"/>
   </bookViews>
@@ -1065,7 +1065,47 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2870,13 +2910,14 @@
   <autoFilter ref="A1:F62" xr:uid="{BF958A36-346A-4392-A336-5806CB7B488B}"/>
   <phoneticPr fontId="19" type="noConversion"/>
   <conditionalFormatting sqref="A1:A1048576">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1:H1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
